--- a/StructureDefinition-ContactadoLE.xlsx
+++ b/StructureDefinition-ContactadoLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
